--- a/Stocks.xlsx
+++ b/Stocks.xlsx
@@ -1,129 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\AI_trader2\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384491A0-F8F7-4334-B97E-57DFF8AE89A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="19260" yWindow="4600" windowWidth="20420" windowHeight="15370" xr2:uid="{4BE74A96-24F1-49CA-A642-8227881FD3BF}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="13040" yWindow="4910" windowWidth="20420" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="stock name" sheetId="1" r:id="rId1"/>
-    <sheet name="options" sheetId="2" r:id="rId2"/>
+    <sheet name="stock name" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="options" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'stock name'!$A$1:$C$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
-  <si>
-    <t>stock name</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>QQQ</t>
-  </si>
-  <si>
-    <t>Local_rule</t>
-  </si>
-  <si>
-    <t>Period</t>
-  </si>
-  <si>
-    <t>1 year</t>
-  </si>
-  <si>
-    <t>1 month</t>
-  </si>
-  <si>
-    <t>3 month</t>
-  </si>
-  <si>
-    <t>6 month</t>
-  </si>
-  <si>
-    <t>year to date</t>
-  </si>
-  <si>
-    <t>2 year</t>
-  </si>
-  <si>
-    <t>5 year</t>
-  </si>
-  <si>
-    <t>max</t>
-  </si>
-  <si>
-    <t>rule 1</t>
-  </si>
-  <si>
-    <t>rule 2</t>
-  </si>
-  <si>
-    <t>rule 3</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Georgia"/>
       <family val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -141,26 +68,91 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -480,129 +472,192 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE051D5-40A7-4370-B0E5-1910CB7C1FA6}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="31.5" customHeight="1" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="16.5" defaultRowHeight="31.5" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="3" width="55.5" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="16.5" style="1"/>
+    <col width="20" customWidth="1" style="1" min="1" max="2"/>
+    <col width="55.5" customWidth="1" style="1" min="3" max="3"/>
+    <col width="16.5" customWidth="1" style="1" min="4" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
+    <row r="1" ht="31.5" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>stock name</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Local_rule</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>AI_Analysis</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Last_Update</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="31.5" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>1 year</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>## 📌 量價階段判定：【第五階段 - 頂部確認】  -   **位階**: 頂部 (已逼近52週高點，RSI過熱) -   **價格動能**: 價跌 (2026年5月14日小幅回落，漲勢放緩) - ...</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15 09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>1 year</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>作為一名頂尖量化股市分析師，我將根據提供的圖表和「Dee's Stock Rule (量價八階律與決策矩陣)」對微軟 (MSFT) 股票進行深度分析。  ## 📌 量價階段判定：【第四階段 - 高位背...</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15 09:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>6 month</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>## 📌 量價階段判定：【第四階段 - 高位背離】  - **位階**: 頂部 (處於歷史新高區間，RSI嚴重超買) - **價格動能**: 價漲 (當日上漲0.71%) - **量能變化**: 量縮...</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15 09:11</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C4" xr:uid="{DEE051D5-40A7-4370-B0E5-1910CB7C1FA6}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <autoFilter ref="A1:C4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0FC1B0B5-E88B-4579-ADDE-C56667C39A84}">
-          <x14:formula1>
-            <xm:f>options!$A$1:$A$8</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B4</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43C81E8-68CB-4B71-A442-5D6D3C4B3978}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="12" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="8.6640625" style="2"/>
+    <col width="12" customWidth="1" style="2" min="1" max="1"/>
+    <col width="8.6640625" customWidth="1" style="2" min="2" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>1 month</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>3 month</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>6 month</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>year to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1 year</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2 year</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5 year</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>